--- a/filer/43910515_harboe.xlsx
+++ b/filer/43910515_harboe.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4161,6 +4162,148 @@
       </c>
       <c r="F86" s="13">
         <f>IFERROR($F$26/($F$48+$F$55)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B89" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C89" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D89" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E89" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F89" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B90" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C90" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D90" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E90" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B91" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C91" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D91" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E91" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F91" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B92" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C92" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D92" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E92" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B93">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C93">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E93">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F93">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4209,346 +4352,346 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1328184</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1419353</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1621066</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1817069</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>1822588</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>1105266</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>1161534</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>1349830</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>1464255</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>1466556</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>222918</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>257819</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>271236</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>352814</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>356032</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>165277</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>202934</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>212175</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>197982</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>211238</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>57658</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>60161</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>65099</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>81369</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>90693</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>13323</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>10802</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>10811</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>9805</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>15851</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>3280</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>6322</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>7736</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>6165</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>6184</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>10026</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>-796</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>-2963</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>77103</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>63768</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>138</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>206</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1957</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>806</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>1875</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>6921</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>6367</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>8015</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>10037</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>9497</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>3243</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>-6957</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>-9021</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>67872</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>56146</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>1584</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-2730</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-4683</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>13111</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>11350</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1659</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>-4227</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>-4338</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>54761</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>44796</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>45400</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>49452</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>61517</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>129245</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>115705</v>
       </c>
     </row>
@@ -4597,832 +4740,832 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>13421</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>6218</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>4202</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>3982</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>3783</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>667947</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>613578</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>589011</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>636873</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>739302</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>5885</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>2363</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>1538</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1538</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>1538</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>706954</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>653619</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>622801</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>667650</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>766712</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>144726</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>164926</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>205368</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>194416</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>199459</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>264396</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>271883</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>355541</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>418227</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>419674</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n">
         <v>6504</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>6572</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>4573</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>4757</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>16642</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>46090</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>9365</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>33132</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>30441</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>434115</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>489403</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>576846</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>652776</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>654331</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>1141069</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>1143022</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>1199647</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>1320426</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>1421043</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>-1275</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>-225</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>-180</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>-9</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <v>224</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>621067</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>621128</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>616814</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>659575</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>695926</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>679792</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>680903</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>676634</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>731566</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>768150</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>44629</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>46453</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>43380</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>42656</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>47729</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>44629</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>46453</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>43380</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>42656</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>47729</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>39907</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>33029</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>35342</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>33435</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>31999</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>86301</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>70318</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>54175</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>36441</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>67153</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>191687</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>167172</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>54757</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>178075</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>16199</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>91427</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>23316</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>73933</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>9996</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>9683</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>10813</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>10886</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>12135</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>117908</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>158597</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>145121</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>244505</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>254769</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>122044</v>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>107808</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>109402</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>110011</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="17" t="n">
         <v>115928</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n">
         <v>2869</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>2426</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>2121</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>1833</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>269590</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>294947</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>375332</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>408645</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>474818</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>461277</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>462119</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>523013</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>588860</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>652893</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>1141069</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>1143022</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>1199647</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>1320426</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="17" t="n">
         <v>1421043</v>
       </c>
     </row>
@@ -5432,6 +5575,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>21402</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>100134</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>-58785</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>182011</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>86120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-36256</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-47119</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-57066</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-127041</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-99591</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-14180</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-23384</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>78838</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-31257</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>10725</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
